--- a/xls/square_un_16_tri3_16.xlsx
+++ b/xls/square_un_16_tri3_16.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>340</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>256</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1362</v>
+      </c>
+      <c r="I14">
+        <v>-0.00019690246674299762</v>
+      </c>
+      <c r="J14">
+        <v>-1.0105715684395897</v>
+      </c>
+      <c r="K14">
+        <v>1.4273721344822965</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>340</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>340</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>297</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1596</v>
+      </c>
+      <c r="I15">
+        <v>-0.00018342508170264872</v>
+      </c>
+      <c r="J15">
+        <v>-0.8520739218947598</v>
+      </c>
+      <c r="K15">
+        <v>1.7165038390563612</v>
+      </c>
+    </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-2.0524760750011506</v>
+        <v>-0.00014750361312587256</v>
       </c>
       <c r="J16">
-        <v>-2.101626300195746</v>
+        <v>-0.5812939963920744</v>
       </c>
       <c r="K16">
-        <v>-0.8353368566857429</v>
+        <v>2.4347640150612646</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.60560216665519</v>
+        <v>-0.00011495384212658816</v>
       </c>
       <c r="J17">
-        <v>-2.212521513420963</v>
+        <v>-0.3969691304099504</v>
       </c>
       <c r="K17">
-        <v>-0.6108946168243499</v>
+        <v>2.813478659935094</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-2.655703472254817</v>
+        <v>-1.2063037316528029e-5</v>
       </c>
       <c r="J18">
-        <v>-2.1609986512043315</v>
+        <v>-0.03523203094886908</v>
       </c>
       <c r="K18">
-        <v>-0.15043271787443682</v>
+        <v>3.324472753596561</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-1.9901228680908192</v>
+        <v>-3.5193337382055496e-8</v>
       </c>
       <c r="J19">
-        <v>-1.671525103348723</v>
+        <v>-8.270531337938288e-5</v>
       </c>
       <c r="K19">
-        <v>0.7091385212148374</v>
+        <v>2.364787175677173</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-0.08851148656310175</v>
+        <v>-2.5240252698409313e-9</v>
       </c>
       <c r="J20">
-        <v>-0.08563033838970749</v>
+        <v>-3.989568760222361e-6</v>
       </c>
       <c r="K20">
-        <v>3.1189289554453983</v>
+        <v>1.7169431445140355</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-0.05692024056697046</v>
+        <v>-1.9020160178208837e-9</v>
       </c>
       <c r="J21">
-        <v>-0.0577959498502644</v>
+        <v>-2.9834458649403485e-6</v>
       </c>
       <c r="K21">
-        <v>3.1631849978872775</v>
+        <v>1.657371234415979</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-0.0006334697308541105</v>
+        <v>-7.795539832287372e-10</v>
       </c>
       <c r="J22">
-        <v>-0.0006593542885765119</v>
+        <v>-1.44345979785601e-6</v>
       </c>
       <c r="K22">
-        <v>2.8501502553597806</v>
+        <v>1.5217404062689261</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-5.867211820899375e-5</v>
+        <v>-4.823050075183051e-10</v>
       </c>
       <c r="J23">
-        <v>-7.042922847303636e-5</v>
+        <v>-8.638620374313872e-7</v>
       </c>
       <c r="K23">
-        <v>2.408533033912815</v>
+        <v>1.4099061054410276</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-3.848061059709856e-5</v>
+        <v>-4.95164266082891e-10</v>
       </c>
       <c r="J24">
-        <v>-4.218945721341832e-5</v>
+        <v>-8.946093700998539e-7</v>
       </c>
       <c r="K24">
-        <v>2.288086847108943</v>
+        <v>1.418713932909708</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-2.461668135938069e-5</v>
+        <v>-3.6465406706893664e-10</v>
       </c>
       <c r="J25">
-        <v>-2.6808964301133327e-5</v>
+        <v>-6.768618226597149e-7</v>
       </c>
       <c r="K25">
-        <v>2.1844586449706616</v>
+        <v>1.3614644985716575</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.7597234640571178e-5</v>
+        <v>-3.285027803774574e-10</v>
       </c>
       <c r="J26">
-        <v>-1.9505248333933584e-5</v>
+        <v>-6.150208082851702e-7</v>
       </c>
       <c r="K26">
-        <v>2.119670110441029</v>
+        <v>1.342601985326446</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.369121050778581e-5</v>
+        <v>-3.051854868683075e-10</v>
       </c>
       <c r="J27">
-        <v>-1.4734480964591428e-5</v>
+        <v>-5.717325244160418e-7</v>
       </c>
       <c r="K27">
-        <v>2.0520050365699984</v>
+        <v>1.3264863969426908</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.0585903542883448e-5</v>
+        <v>-2.7667037187959825e-10</v>
       </c>
       <c r="J28">
-        <v>-1.1339026025863825e-5</v>
+        <v>-5.080275116818649e-7</v>
       </c>
       <c r="K28">
-        <v>1.9948624458132849</v>
+        <v>1.2993001599001004</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-9.301325925466504e-6</v>
+        <v>-2.859827375810157e-10</v>
       </c>
       <c r="J29">
-        <v>-9.696464466529604e-6</v>
+        <v>-5.324771034631479e-7</v>
       </c>
       <c r="K29">
-        <v>1.9528032291375788</v>
+        <v>1.3100171556020255</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-8.863228296557302e-6</v>
+        <v>-2.588556755497492e-10</v>
       </c>
       <c r="J30">
-        <v>-9.389528843658362e-6</v>
+        <v>-4.818647579734746e-7</v>
       </c>
       <c r="K30">
-        <v>1.9487141900757912</v>
+        <v>1.2889804365904127</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-4.924893619810168e-6</v>
+        <v>-2.259766894773957e-10</v>
       </c>
       <c r="J31">
-        <v>-5.338658429585549e-6</v>
+        <v>-4.299742445972539e-7</v>
       </c>
       <c r="K31">
-        <v>1.8349564835462473</v>
+        <v>1.2658994221534512</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-5.5732066893538856e-6</v>
+        <v>-2.2057877004784186e-10</v>
       </c>
       <c r="J32">
-        <v>-5.8396507908210966e-6</v>
+        <v>-4.1410094873155597e-7</v>
       </c>
       <c r="K32">
-        <v>1.8452210383308367</v>
+        <v>1.256994156254369</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_16.xlsx
+++ b/xls/square_un_16_tri3_16.xlsx
@@ -482,13 +482,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.00019690246674299762</v>
+        <v>-1.4833053284126763</v>
       </c>
       <c r="J14">
-        <v>-1.0105715684395897</v>
+        <v>-1.869924692165987</v>
       </c>
       <c r="K14">
-        <v>1.4273721344822965</v>
+        <v>-0.8168152514382024</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00018342508170264872</v>
+        <v>-2.2079560564464646</v>
       </c>
       <c r="J15">
-        <v>-0.8520739218947598</v>
+        <v>-1.9284282837336773</v>
       </c>
       <c r="K15">
-        <v>1.7165038390563612</v>
+        <v>-0.6631861798496131</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-0.00014750361312587256</v>
+        <v>-2.290722620051434</v>
       </c>
       <c r="J16">
-        <v>-0.5812939963920744</v>
+        <v>-1.9714769052155</v>
       </c>
       <c r="K16">
-        <v>2.4347640150612646</v>
+        <v>-0.7821366744612385</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-0.00011495384212658816</v>
+        <v>-1.4571168620357609</v>
       </c>
       <c r="J17">
-        <v>-0.3969691304099504</v>
+        <v>-1.2808254527411658</v>
       </c>
       <c r="K17">
-        <v>2.813478659935094</v>
+        <v>0.6220836678942769</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-1.2063037316528029e-5</v>
+        <v>-0.6472349001850435</v>
       </c>
       <c r="J18">
-        <v>-0.03523203094886908</v>
+        <v>-0.5676555419755961</v>
       </c>
       <c r="K18">
-        <v>3.324472753596561</v>
+        <v>1.7670001624845169</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-3.5193337382055496e-8</v>
+        <v>-0.08887741347915865</v>
       </c>
       <c r="J19">
-        <v>-8.270531337938288e-5</v>
+        <v>-0.08378827667338251</v>
       </c>
       <c r="K19">
-        <v>2.364787175677173</v>
+        <v>2.540636206282954</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-2.5240252698409313e-9</v>
+        <v>1.1519521755973192e-6</v>
       </c>
       <c r="J20">
-        <v>-3.989568760222361e-6</v>
+        <v>-3.6660936447715006e-6</v>
       </c>
       <c r="K20">
-        <v>1.7169431445140355</v>
+        <v>1.9478681849036361</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.9020160178208837e-9</v>
+        <v>1.1550306917287577e-6</v>
       </c>
       <c r="J21">
-        <v>-2.9834458649403485e-6</v>
+        <v>-2.0659946959540066e-6</v>
       </c>
       <c r="K21">
-        <v>1.657371234415979</v>
+        <v>1.8415333133404048</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-7.795539832287372e-10</v>
+        <v>-1.0346429720939426e-6</v>
       </c>
       <c r="J22">
-        <v>-1.44345979785601e-6</v>
+        <v>-1.5728048059657586e-6</v>
       </c>
       <c r="K22">
-        <v>1.5217404062689261</v>
+        <v>1.6184178620978777</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-4.823050075183051e-10</v>
+        <v>-8.257030540868806e-7</v>
       </c>
       <c r="J23">
-        <v>-8.638620374313872e-7</v>
+        <v>-9.09290336067696e-7</v>
       </c>
       <c r="K23">
-        <v>1.4099061054410276</v>
+        <v>1.4495156917784504</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-4.95164266082891e-10</v>
+        <v>-8.805553366412665e-7</v>
       </c>
       <c r="J24">
-        <v>-8.946093700998539e-7</v>
+        <v>-9.099656512817622e-7</v>
       </c>
       <c r="K24">
-        <v>1.418713932909708</v>
+        <v>1.4368898494872724</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-3.6465406706893664e-10</v>
+        <v>-7.05885572839528e-7</v>
       </c>
       <c r="J25">
-        <v>-6.768618226597149e-7</v>
+        <v>-7.227251636172892e-7</v>
       </c>
       <c r="K25">
-        <v>1.3614644985716575</v>
+        <v>1.3828932652753014</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.285027803774574e-10</v>
+        <v>-5.899176260222884e-7</v>
       </c>
       <c r="J26">
-        <v>-6.150208082851702e-7</v>
+        <v>-6.242413325339511e-7</v>
       </c>
       <c r="K26">
-        <v>1.342601985326446</v>
+        <v>1.3606216776234445</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.051854868683075e-10</v>
+        <v>-6.562530449317177e-7</v>
       </c>
       <c r="J27">
-        <v>-5.717325244160418e-7</v>
+        <v>-6.325543903369203e-7</v>
       </c>
       <c r="K27">
-        <v>1.3264863969426908</v>
+        <v>1.3390327937693969</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-2.7667037187959825e-10</v>
+        <v>-5.913324638435309e-7</v>
       </c>
       <c r="J28">
-        <v>-5.080275116818649e-7</v>
+        <v>-5.643560330381747e-7</v>
       </c>
       <c r="K28">
-        <v>1.2993001599001004</v>
+        <v>1.314149167640076</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-2.859827375810157e-10</v>
+        <v>-6.191738406632201e-7</v>
       </c>
       <c r="J29">
-        <v>-5.324771034631479e-7</v>
+        <v>-5.888965598062983e-7</v>
       </c>
       <c r="K29">
-        <v>1.3100171556020255</v>
+        <v>1.3214096346044577</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.588556755497492e-10</v>
+        <v>-5.841555372220113e-7</v>
       </c>
       <c r="J30">
-        <v>-4.818647579734746e-7</v>
+        <v>-5.45806327736268e-7</v>
       </c>
       <c r="K30">
-        <v>1.2889804365904127</v>
+        <v>1.3003855469033816</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-2.259766894773957e-10</v>
+        <v>-5.372682905833941e-7</v>
       </c>
       <c r="J31">
-        <v>-4.299742445972539e-7</v>
+        <v>-5.008388773183156e-7</v>
       </c>
       <c r="K31">
-        <v>1.2658994221534512</v>
+        <v>1.2799647348730028</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-2.2057877004784186e-10</v>
+        <v>-4.916153713336916e-7</v>
       </c>
       <c r="J32">
-        <v>-4.1410094873155597e-7</v>
+        <v>-4.65593325906991e-7</v>
       </c>
       <c r="K32">
-        <v>1.256994156254369</v>
+        <v>1.2704533065250392</v>
       </c>
     </row>
   </sheetData>
